--- a/demo/kampung_makmur_sdn_bhd/kampung_makmur_sdn_bhd_data.xlsx
+++ b/demo/kampung_makmur_sdn_bhd/kampung_makmur_sdn_bhd_data.xlsx
@@ -525,7 +525,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-06T08:53:30Z</t>
+          <t>2026-10-06T10:36:40Z</t>
         </is>
       </c>
     </row>
@@ -2143,7 +2143,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-10-06T08:53:30Z</t>
+          <t>2026-10-06T10:36:40Z</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>

--- a/demo/kampung_makmur_sdn_bhd/kampung_makmur_sdn_bhd_data.xlsx
+++ b/demo/kampung_makmur_sdn_bhd/kampung_makmur_sdn_bhd_data.xlsx
@@ -13,16 +13,18 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gap Analysis" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Claims" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All figures" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Methodology" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AI provenance" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Methodology" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Summary'!$A$3:$B$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Summary'!$A$3:$B$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'5 Dimensions'!$A$1:$E$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'SDG Alignment'!$A$1:$G$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Gap Analysis'!$A$1:$F$18</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Claims'!$A$1:$E$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'All figures'!$A$1:$G$55</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Methodology'!$A$1:$B$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Claims'!$A$1:$F$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'All figures'!$A$1:$G$57</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'AI provenance'!$A$13:$F$37</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Methodology'!$A$1:$B$12</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -455,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -525,7 +527,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-06T10:36:40Z</t>
+          <t>2026-10-07T00:37:32Z</t>
         </is>
       </c>
     </row>
@@ -620,17 +622,53 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>AI disclosure</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Automated analysis: produced by rules and a deterministic scoring model; no generative AI was used. 4 of 22 scores are estimated from document text rather than reported metrics. Review before relying on it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Methodology version</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>1.1.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Methodology config hash</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>8fabf9b5a7e2</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>Export schema</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:B16"/>
+  <autoFilter ref="A3:B19"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -861,15 +899,15 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Zero Hunger</t>
+          <t>Affordable and Clean Energy</t>
         </is>
       </c>
       <c r="C2" s="4" t="n">
-        <v>35</v>
+        <v>43.3</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -881,24 +919,28 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>OI2496, OI2764</t>
+        </is>
+      </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2.1, 2.3, 2.4</t>
+          <t>7.1, 7.2, 7.3</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Climate Action</t>
+          <t>Zero Hunger</t>
         </is>
       </c>
       <c r="C3" s="4" t="n">
-        <v>35</v>
+        <v>41.7</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,24 +952,28 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>PI9991</t>
+        </is>
+      </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>13.1, 13.2, 13.3</t>
+          <t>2.1, 2.3, 2.4</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Decent Work and Economic Growth</t>
+          <t>Climate Action</t>
         </is>
       </c>
       <c r="C4" s="4" t="n">
-        <v>33.5</v>
+        <v>41.7</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -941,12 +987,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>OI6213, OI8869</t>
+          <t>OI2764</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>8.1, 8.2, 8.3, 8.4, 8.5, 8.6, 8.7, 8.8</t>
+          <t>13.1, 13.2, 13.3</t>
         </is>
       </c>
     </row>
@@ -1006,15 +1052,15 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Clean Water and Sanitation</t>
+          <t>Decent Work and Economic Growth</t>
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>30</v>
+        <v>32.3</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1026,16 +1072,24 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>OI6213, OI8869</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>8.1, 8.2, 8.3, 8.4, 8.5, 8.6, 8.7, 8.8</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Affordable and Clean Energy</t>
+          <t>Clean Water and Sanitation</t>
         </is>
       </c>
       <c r="C8" s="4" t="n">
@@ -1052,11 +1106,7 @@
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>7.1, 7.2, 7.3</t>
-        </is>
-      </c>
+      <c r="G8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1089,15 +1139,15 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Industry, Innovation and Infrastructure</t>
+          <t>Good Health and Well-being</t>
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1109,24 +1159,16 @@
           <t>no</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>OI8869</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>9.3, 9.4</t>
-        </is>
-      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Good Health and Well-being</t>
+          <t>Partnerships for the Goals</t>
         </is>
       </c>
       <c r="C11" s="4" t="n">
@@ -1139,7 +1181,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
@@ -1147,15 +1189,15 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Partnerships for the Goals</t>
+          <t>Industry, Innovation and Infrastructure</t>
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>17.5</v>
+        <v>14</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1164,23 +1206,31 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>OI8869</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>9.3, 9.4</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Reduced Inequalities</t>
+          <t>Gender Equality</t>
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>14.8</v>
+        <v>10.2</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1199,21 +1249,21 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>10.1, 10.2, 10.3</t>
+          <t>5.1, 5.2, 5.5</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Gender Equality</t>
+          <t>Reduced Inequalities</t>
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>13.5</v>
+        <v>10</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1225,14 +1275,10 @@
           <t>no</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>OI6213</t>
-        </is>
-      </c>
+      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>5.1, 5.2, 5.5</t>
+          <t>10.1, 10.2, 10.3</t>
         </is>
       </c>
     </row>
@@ -1811,7 +1857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1819,6 +1865,7 @@
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1847,6 +1894,11 @@
           <t>Mapped metrics</t>
         </is>
       </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>Extracted by</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1866,6 +1918,11 @@
         <v>0.3</v>
       </c>
       <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>regex</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1889,6 +1946,11 @@
           <t>OI2496, OI2764</t>
         </is>
       </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>regex</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1908,6 +1970,11 @@
         <v>0.35</v>
       </c>
       <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>regex</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1931,6 +1998,11 @@
           <t>OI8869, OI6213</t>
         </is>
       </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>regex</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1954,6 +2026,11 @@
           <t>PI9991</t>
         </is>
       </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>regex</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1973,6 +2050,11 @@
         <v>0.35</v>
       </c>
       <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>regex</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1992,6 +2074,11 @@
         <v>0.3</v>
       </c>
       <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>regex</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2011,6 +2098,11 @@
         <v>0.3</v>
       </c>
       <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>regex</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2030,6 +2122,11 @@
         <v>0.3</v>
       </c>
       <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>regex</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2049,9 +2146,14 @@
         <v>0.3</v>
       </c>
       <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>regex</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E11"/>
+  <autoFilter ref="A1:F11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2062,7 +2164,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G55"/>
+  <dimension ref="A1:G57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2143,7 +2245,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-10-06T10:36:40Z</t>
+          <t>2026-10-07T00:37:32Z</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
@@ -2152,68 +2254,44 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>5D</t>
+          <t>Company</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Overall Grade</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>1.7/5.0</t>
-        </is>
-      </c>
-      <c r="E4" s="5" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>score</t>
-        </is>
-      </c>
+          <t>AI disclosure</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Automated analysis: produced by rules and a deterministic scoring model; no generative AI was used. 4 of 22 scores are estimated from document text rather than reported metrics. Review before relying on it.</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>5D</t>
+          <t>Company</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>What</t>
+          <t>Methodology</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2.3/5.0</t>
+          <t>1.1.0</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Reporting 2 metrics (1 theme-specific, 25 available)</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="F5" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>score</t>
-        </is>
-      </c>
+          <t>config 8fabf9b5a7e2</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2223,21 +2301,21 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Who</t>
+          <t>Overall Grade</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2.3/5.0</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Reporting 3 metrics (1 theme-specific, 10 available)</t>
+          <t>1.7/5.0</t>
         </is>
       </c>
       <c r="E6" s="5" t="n">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="F6" s="6" t="n">
         <v>5</v>
@@ -2256,21 +2334,21 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>How Much</t>
+          <t>What</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.5/5.0</t>
+          <t>2.3/5.0</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Scale=1.5, Depth=1.5, Duration=1.5</t>
+          <t>Reporting 2 metrics (1 theme-specific, 25 available)</t>
         </is>
       </c>
       <c r="E7" s="5" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="F7" s="6" t="n">
         <v>5</v>
@@ -2289,21 +2367,21 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Contribution</t>
+          <t>Who</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.3/5.0</t>
+          <t>2.3/5.0</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Depth=1.3, Duration=1.3</t>
+          <t>Reporting 3 metrics (1 theme-specific, 10 available)</t>
         </is>
       </c>
       <c r="E8" s="5" t="n">
-        <v>1.3</v>
+        <v>2.3</v>
       </c>
       <c r="F8" s="6" t="n">
         <v>5</v>
@@ -2322,21 +2400,21 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Risk</t>
+          <t>How Much</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.3/5.0</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>Estimated from sector/description (4 metrics available to track)</t>
+          <t>1.5/5.0</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Scale=1.5, Depth=1.5, Duration=1.5</t>
         </is>
       </c>
       <c r="E9" s="5" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="F9" s="6" t="n">
         <v>5</v>
@@ -2350,29 +2428,29 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SDG</t>
+          <t>5D</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SDG 2</t>
+          <t>Contribution</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>35.0/100</t>
+          <t>1.3/5.0</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">medium | metrics: </t>
+          <t>Depth=1.3, Duration=1.3</t>
         </is>
       </c>
       <c r="E10" s="5" t="n">
-        <v>35</v>
+        <v>1.3</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -2383,29 +2461,29 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SDG</t>
+          <t>5D</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SDG 13</t>
+          <t>Risk</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>35.0/100</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">medium | metrics: </t>
+          <t>1.3/5.0</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Estimated from sector/description (4 metrics available to track)</t>
         </is>
       </c>
       <c r="E11" s="5" t="n">
-        <v>35</v>
+        <v>1.3</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -2421,21 +2499,21 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SDG 8</t>
+          <t>SDG 7</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>33.5/100</t>
+          <t>43.3/100</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>medium | metrics: OI6213,OI8869</t>
+          <t>medium | metrics: OI2496,OI2764</t>
         </is>
       </c>
       <c r="E12" s="5" t="n">
-        <v>33.5</v>
+        <v>43.3</v>
       </c>
       <c r="F12" s="6" t="n">
         <v>100</v>
@@ -2454,21 +2532,21 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SDG 12</t>
+          <t>SDG 2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>32.5/100</t>
+          <t>41.7/100</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">medium | metrics: </t>
+          <t>medium | metrics: PI9991</t>
         </is>
       </c>
       <c r="E13" s="5" t="n">
-        <v>32.5</v>
+        <v>41.7</v>
       </c>
       <c r="F13" s="6" t="n">
         <v>100</v>
@@ -2487,21 +2565,21 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SDG 15</t>
+          <t>SDG 13</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>32.5/100</t>
+          <t>41.7/100</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">medium | metrics: </t>
+          <t>medium | metrics: OI2764</t>
         </is>
       </c>
       <c r="E14" s="5" t="n">
-        <v>32.5</v>
+        <v>41.7</v>
       </c>
       <c r="F14" s="6" t="n">
         <v>100</v>
@@ -2520,12 +2598,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SDG 6</t>
+          <t>SDG 12</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>30.0/100</t>
+          <t>32.5/100</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2534,7 +2612,7 @@
         </is>
       </c>
       <c r="E15" s="5" t="n">
-        <v>30</v>
+        <v>32.5</v>
       </c>
       <c r="F15" s="6" t="n">
         <v>100</v>
@@ -2553,12 +2631,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SDG 7</t>
+          <t>SDG 15</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>30.0/100</t>
+          <t>32.5/100</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2567,7 +2645,7 @@
         </is>
       </c>
       <c r="E16" s="5" t="n">
-        <v>30</v>
+        <v>32.5</v>
       </c>
       <c r="F16" s="6" t="n">
         <v>100</v>
@@ -2586,21 +2664,21 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SDG 1</t>
+          <t>SDG 8</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>25.0/100</t>
+          <t>32.3/100</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">medium | metrics: </t>
+          <t>medium | metrics: OI6213,OI8869</t>
         </is>
       </c>
       <c r="E17" s="5" t="n">
-        <v>25</v>
+        <v>32.3</v>
       </c>
       <c r="F17" s="6" t="n">
         <v>100</v>
@@ -2619,21 +2697,21 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SDG 9</t>
+          <t>SDG 6</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>18.0/100</t>
+          <t>30.0/100</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>low | metrics: OI8869</t>
+          <t xml:space="preserve">medium | metrics: </t>
         </is>
       </c>
       <c r="E18" s="5" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="F18" s="6" t="n">
         <v>100</v>
@@ -2652,21 +2730,21 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SDG 3</t>
+          <t>SDG 1</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>17.5/100</t>
+          <t>25.0/100</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">low | metrics: </t>
+          <t xml:space="preserve">medium | metrics: </t>
         </is>
       </c>
       <c r="E19" s="5" t="n">
-        <v>17.5</v>
+        <v>25</v>
       </c>
       <c r="F19" s="6" t="n">
         <v>100</v>
@@ -2685,7 +2763,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SDG 17</t>
+          <t>SDG 3</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2718,21 +2796,21 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SDG 10</t>
+          <t>SDG 17</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>14.8/100</t>
+          <t>17.5/100</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>low | metrics: OI6213</t>
+          <t xml:space="preserve">low | metrics: </t>
         </is>
       </c>
       <c r="E21" s="5" t="n">
-        <v>14.8</v>
+        <v>17.5</v>
       </c>
       <c r="F21" s="6" t="n">
         <v>100</v>
@@ -2751,21 +2829,21 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SDG 5</t>
+          <t>SDG 9</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>13.5/100</t>
+          <t>14.0/100</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>low | metrics: OI6213</t>
+          <t>low | metrics: OI8869</t>
         </is>
       </c>
       <c r="E22" s="5" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="F22" s="6" t="n">
         <v>100</v>
@@ -2784,21 +2862,21 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SDG 11</t>
+          <t>SDG 5</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>10.0/100</t>
+          <t>10.2/100</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">low | metrics: </t>
+          <t>low | metrics: OI6213</t>
         </is>
       </c>
       <c r="E23" s="5" t="n">
-        <v>10</v>
+        <v>10.2</v>
       </c>
       <c r="F23" s="6" t="n">
         <v>100</v>
@@ -2817,7 +2895,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>SDG 14</t>
+          <t>SDG 10</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2850,7 +2928,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>SDG 16</t>
+          <t>SDG 11</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2883,12 +2961,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>SDG 4</t>
+          <t>SDG 14</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>5.0/100</t>
+          <t>10.0/100</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2897,7 +2975,7 @@
         </is>
       </c>
       <c r="E26" s="5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F26" s="6" t="n">
         <v>100</v>
@@ -2911,87 +2989,101 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Greenwashing</t>
+          <t>SDG</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Risk score</t>
+          <t>SDG 16</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>49.0/100</t>
+          <t>10.0/100</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Moderate Risk</t>
+          <t xml:space="preserve">low | metrics: </t>
         </is>
       </c>
       <c r="E27" s="5" t="n">
-        <v>49</v>
+        <v>10</v>
       </c>
       <c r="F27" s="6" t="n">
         <v>100</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>risk</t>
+          <t>score</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Gap</t>
+          <t>SDG</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Coverage</t>
+          <t>SDG 4</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>17.6%</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
+          <t>5.0/100</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">low | metrics: </t>
+        </is>
+      </c>
       <c r="E28" s="5" t="n">
-        <v>17.6</v>
+        <v>5</v>
       </c>
       <c r="F28" s="6" t="n">
         <v>100</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>score</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gap</t>
+          <t>Greenwashing</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>OD4091</t>
+          <t>Risk score</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>49.0/100</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Social and Environmental Targets</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr"/>
+          <t>Moderate Risk</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>49</v>
+      </c>
+      <c r="F29" s="6" t="n">
+        <v>100</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>risk</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -3001,20 +3093,26 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>OI0263</t>
+          <t>Coverage</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>MISSING</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Water Withdrawn</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr"/>
+          <t>17.6%</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" s="5" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="F30" s="6" t="n">
+        <v>100</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -3024,7 +3122,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>OI1075</t>
+          <t>OD4091</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -3034,7 +3132,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Board of Directors: Total</t>
+          <t>Social and Environmental Targets</t>
         </is>
       </c>
       <c r="G31" t="inlineStr"/>
@@ -3047,7 +3145,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>OI1479</t>
+          <t>OI0263</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -3057,7 +3155,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Greenhouse Gas Emissions: Total</t>
+          <t>Water Withdrawn</t>
         </is>
       </c>
       <c r="G32" t="inlineStr"/>
@@ -3070,7 +3168,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>OI1571</t>
+          <t>OI1075</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -3080,7 +3178,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Full-time Employees: Female Managers</t>
+          <t>Board of Directors: Total</t>
         </is>
       </c>
       <c r="G33" t="inlineStr"/>
@@ -3093,7 +3191,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>OI1582</t>
+          <t>OI1479</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -3103,7 +3201,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Wage Equity</t>
+          <t>Greenhouse Gas Emissions: Total</t>
         </is>
       </c>
       <c r="G34" t="inlineStr"/>
@@ -3116,7 +3214,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>OI3757</t>
+          <t>OI1571</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -3126,7 +3224,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Occupational Injuries</t>
+          <t>Full-time Employees: Female Managers</t>
         </is>
       </c>
       <c r="G35" t="inlineStr"/>
@@ -3139,7 +3237,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>OI4112</t>
+          <t>OI1582</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -3149,7 +3247,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Greenhouse Gas Emissions: Direct (Scope 1)</t>
+          <t>Wage Equity</t>
         </is>
       </c>
       <c r="G36" t="inlineStr"/>
@@ -3162,7 +3260,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>OI4724</t>
+          <t>OI3757</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -3172,7 +3270,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Workers Earning a Living Wage or Higher</t>
+          <t>Occupational Injuries</t>
         </is>
       </c>
       <c r="G37" t="inlineStr"/>
@@ -3185,7 +3283,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>OI4732</t>
+          <t>OI4112</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -3195,7 +3293,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Social and Environmental Performance Reporting</t>
+          <t>Greenhouse Gas Emissions: Direct (Scope 1)</t>
         </is>
       </c>
       <c r="G38" t="inlineStr"/>
@@ -3208,7 +3306,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>OI6709</t>
+          <t>OI4724</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -3218,7 +3316,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Waste Produced: Total</t>
+          <t>Workers Earning a Living Wage or Higher</t>
         </is>
       </c>
       <c r="G39" t="inlineStr"/>
@@ -3231,7 +3329,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>OI6912</t>
+          <t>OI4732</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -3241,7 +3339,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Land Directly Controlled: Sustainably Managed</t>
+          <t>Social and Environmental Performance Reporting</t>
         </is>
       </c>
       <c r="G40" t="inlineStr"/>
@@ -3254,7 +3352,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>OI9891</t>
+          <t>OI6709</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3264,7 +3362,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Pesticide Use</t>
+          <t>Waste Produced: Total</t>
         </is>
       </c>
       <c r="G41" t="inlineStr"/>
@@ -3277,7 +3375,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>PI7852</t>
+          <t>OI6912</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3287,7 +3385,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Payments to Supplier Individuals: Smallholder</t>
+          <t>Land Directly Controlled: Sustainably Managed</t>
         </is>
       </c>
       <c r="G42" t="inlineStr"/>
@@ -3300,27 +3398,20 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>OI6213</t>
+          <t>OI9891</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>54 (derived: 38% of 142)</t>
+          <t>MISSING</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Full-time Employees: Female</t>
-        </is>
-      </c>
-      <c r="E43" s="5" t="n">
-        <v>54</v>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>(derived: 38% of 142)</t>
-        </is>
-      </c>
+          <t>Pesticide Use</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -3330,21 +3421,18 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>OI8869</t>
+          <t>PI7852</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>142</t>
+          <t>MISSING</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Permanent Employees: Total</t>
-        </is>
-      </c>
-      <c r="E44" s="5" t="n">
-        <v>142</v>
+          <t>Payments to Supplier Individuals: Smallholder</t>
+        </is>
       </c>
       <c r="G44" t="inlineStr"/>
     </row>
@@ -3356,67 +3444,77 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>PI9991</t>
+          <t>OI6213</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>54 (derived: 38% of 142)</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Supplier Individuals: Smallholder</t>
+          <t>Full-time Employees: Female</t>
         </is>
       </c>
       <c r="E45" s="5" t="n">
-        <v>18</v>
-      </c>
-      <c r="G45" t="inlineStr"/>
+        <v>54</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>(derived: 38% of 142)</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Claim</t>
+          <t>Gap</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>outcome</t>
-        </is>
-      </c>
-      <c r="C46" s="3" t="inlineStr">
-        <is>
-          <t>Since 2022 we have reduced antibiotic use by 62% through vaccination and group-housing, and replaced 100% of conventional slatted housing with deep-litter, enrichment-enabled pens benchmarked against the EU Welfare Quality protocol.</t>
+          <t>OI8869</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>142</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">metrics: </t>
-        </is>
+          <t>Permanent Employees: Total</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="n">
+        <v>142</v>
       </c>
       <c r="G46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Claim</t>
+          <t>Gap</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>outcome</t>
-        </is>
-      </c>
-      <c r="C47" s="3" t="inlineStr">
-        <is>
-          <t>Our biogas plant captures methane from manure lagoons and generates 1.8 GWh of electricity per year, replacing ~920 tonnes CO2e of grid emissions and cutting our grid electricity purchases by 74%.</t>
+          <t>PI9991</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>18</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>metrics: OI2496,OI2764</t>
-        </is>
+          <t>Supplier Individuals: Smallholder</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="n">
+        <v>18</v>
       </c>
       <c r="G47" t="inlineStr"/>
     </row>
@@ -3433,7 +3531,7 @@
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>Water withdrawal per kg of live weight dropped 31% versus our 2020 baseline, independently verified by SIRIM.</t>
+          <t>Since 2022 we have reduced antibiotic use by 62% through vaccination and group-housing, and replaced 100% of conventional slatted housing with deep-litter, enrichment-enabled pens benchmarked against the EU Welfare Quality protocol.</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -3456,12 +3554,12 @@
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>We employ 142 staff, of whom 38% are women and 64% are from Kluang district; median wage is 42% above the Johor agricultural minimum and every worker is enrolled in SOCSO and EPF.</t>
+          <t>Our biogas plant captures methane from manure lagoons and generates 1.8 GWh of electricity per year, replacing ~920 tonnes CO2e of grid emissions and cutting our grid electricity purchases by 74%.</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>metrics: OI8869,OI6213</t>
+          <t>metrics: OI2496,OI2764</t>
         </is>
       </c>
       <c r="G49" t="inlineStr"/>
@@ -3479,12 +3577,12 @@
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>We run an outgrower programme with 18 smallholder piggeries, supplying feed and veterinary support at wholesale cost; participating smallholders report average income uplifts of RM 1,850 per month (baseline: RM 900).</t>
+          <t>Water withdrawal per kg of live weight dropped 31% versus our 2020 baseline, independently verified by SIRIM.</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>metrics: PI9991</t>
+          <t xml:space="preserve">metrics: </t>
         </is>
       </c>
       <c r="G50" t="inlineStr"/>
@@ -3502,12 +3600,12 @@
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>A 2024 randomized pilot with Universiti Putra Malaysia compared 120 outgrower households to a matched control group and found 23% higher household food-security scores and 17% higher child school attendance.</t>
+          <t>We employ 142 staff, of whom 38% are women and 64% are from Kluang district; median wage is 42% above the Johor agricultural minimum and every worker is enrolled in SOCSO and EPF.</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">metrics: </t>
+          <t>metrics: OI8869,OI6213</t>
         </is>
       </c>
       <c r="G51" t="inlineStr"/>
@@ -3520,17 +3618,17 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>intent</t>
+          <t>outcome</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>Over the next five years we target: 45% reduction in Scope 1+2 emissions intensity (kg CO2e / kg live weight); 80% of breeding sows in group-housing &gt;= 10 weeks after weaning; 35 outgrower households onboarded; and a SBTi near-term target submission by 2027.</t>
+          <t>We run an outgrower programme with 18 smallholder piggeries, supplying feed and veterinary support at wholesale cost; participating smallholders report average income uplifts of RM 1,850 per month (baseline: RM 900).</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">metrics: </t>
+          <t>metrics: PI9991</t>
         </is>
       </c>
       <c r="G52" t="inlineStr"/>
@@ -3543,12 +3641,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>output</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>We are SEDEX-audited and have a 4-tier grievance mechanism.</t>
+          <t>outcome</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>A 2024 randomized pilot with Universiti Putra Malaysia compared 120 outgrower households to a matched control group and found 23% higher household food-security scores and 17% higher child school attendance.</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -3566,12 +3664,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>output</t>
+          <t>intent</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>Risks we actively manage include: (i) ASF biosecurity - all farms are fenced, SPF breeding stock, shower-in/out protocol, quarterly third-party audit by the Department of Veterinary Services; (ii) nutrient run-off during monsoon - on-site retention ponds sized to 1-in-100-year storm, automated ammonia sensors; (iii) community odour - a covered-lagoon retrofit was completed in Q3 2025 and the formal complaints rate has dropped from 14 to 2 per year.</t>
+          <t>Over the next five years we target: 45% reduction in Scope 1+2 emissions intensity (kg CO2e / kg live weight); 80% of breeding sows in group-housing &gt;= 10 weeks after weaning; 35 outgrower households onboarded; and a SBTi near-term target submission by 2027.</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3592,20 +3690,66 @@
           <t>output</t>
         </is>
       </c>
-      <c r="C55" s="3" t="inlineStr">
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>We are SEDEX-audited and have a 4-tier grievance mechanism.</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metrics: </t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Claim</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>output</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>Risks we actively manage include: (i) ASF biosecurity - all farms are fenced, SPF breeding stock, shower-in/out protocol, quarterly third-party audit by the Department of Veterinary Services; (ii) nutrient run-off during monsoon - on-site retention ponds sized to 1-in-100-year storm, automated ammonia sensors; (iii) community odour - a covered-lagoon retrofit was completed in Q3 2025 and the formal complaints rate has dropped from 14 to 2 per year.</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metrics: </t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Claim</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>output</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
         <is>
           <t>We report against IRIS+, SDG 2/6/7/8/12/13, GRI standards, and have commissioned a first independent ESG audit for FY2026.</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
+      <c r="D57" t="inlineStr">
         <is>
           <t xml:space="preserve">metrics: </t>
         </is>
       </c>
-      <c r="G55" t="inlineStr"/>
+      <c r="G57" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G55"/>
+  <autoFilter ref="A1:G57"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3616,7 +3760,858 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:F37"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>AI disclosure</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Automated analysis: produced by rules and a deterministic scoring model; no generative AI was used. 4 of 22 scores are estimated from document text rather than reported metrics. Review before relying on it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Claim extraction</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>rules</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Score calculation</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>deterministic</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Metric / SDG tagging</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>rules</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Narrative drafting</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Generative AI used</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Scores estimated from text</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>4 of 22</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Human review</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>not recorded</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Regulation</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>EU AI Act Art 50 transparency (Regulation (EU) 2024/1689 as amended by Regulation (EU) 2026/1744)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Figure</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Stage</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Method</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Estimated</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Five Dimensions: what</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>calculation</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>deterministic</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>evidence: partial</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Five Dimensions: who</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>calculation</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>deterministic</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>evidence: evidence-based</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Five Dimensions: how much</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>calculation</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>deterministic</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>evidence: estimated</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Five Dimensions: contribution</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>calculation</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>deterministic</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>evidence: estimated</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Five Dimensions: risk</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>calculation</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>deterministic</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>evidence: estimated</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>SDG 7 alignment</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>calculation</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>deterministic</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>basis: core_set</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>SDG 2 alignment</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>calculation</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>deterministic</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>basis: core_set</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>SDG 13 alignment</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>calculation</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>deterministic</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>basis: core_set</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>SDG 12 alignment</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>calculation</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>deterministic</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>basis: core_set</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>SDG 15 alignment</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>calculation</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>deterministic</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>basis: core_set</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>SDG 8 alignment</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>calculation</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>deterministic</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>basis: core_set</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>SDG 6 alignment</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>calculation</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>deterministic</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>basis: core_set</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>SDG 1 alignment</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>calculation</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>deterministic</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>basis: core_set</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>SDG 3 alignment</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>calculation</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>deterministic</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>basis: core_set</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>SDG 17 alignment</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>calculation</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>deterministic</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>basis: estimated</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>SDG 9 alignment</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>calculation</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>deterministic</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>basis: core_set</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>SDG 5 alignment</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>calculation</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>deterministic</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>basis: core_set</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>SDG 10 alignment</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>calculation</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>deterministic</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>basis: core_set</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>SDG 11 alignment</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>calculation</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>deterministic</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>basis: core_set</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>SDG 14 alignment</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>calculation</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>deterministic</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>basis: core_set</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>SDG 16 alignment</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>calculation</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>deterministic</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>basis: core_set</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>SDG 4 alignment</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>calculation</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>deterministic</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>basis: core_set</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>10 impact claims</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>extraction</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>rules</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>IRIS+ / SDG mapping of claims</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>tagging</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>rules</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A13:F37"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3655,31 +4650,31 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Scores (1–5) for What, Who, How Much, Contribution and Risk come from reported metrics where available and from document text otherwise.</t>
+          <t>Each dimension scores 1–5: coverage of the theme's IRIS+ reference set × 4.5 + 0.5 when any metric is reported, plus up to 0.5 for extra metrics. A dimension stays at or below 2.5 until 3 metrics hit its reference set; text-only inference is clamped to 0.5–2.5. Grades: A ≥ 4.5, B+ ≥ 3.5, B ≥ 3.0, B- ≥ 2.5, C+ ≥ 2.0, C ≥ 1.5, D ≥ 1.0.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SDGs</t>
+          <t>5D penalties</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Scores (0–100) combine goal-specific metric coverage and inference from the business and impact themes; cross-cutting metrics count at reduced weight. 'Material' marks goals the business model directly drives.</t>
+          <t>Risk loses 0.3 per unmitigated adverse impact (max 1.5) and 0.5 per exclusion flag (max 1.0).</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Gap analysis</t>
+          <t>SDGs</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Coverage is the share of the sector's IRIS+ core metric set the company reports.</t>
+          <t>Each goal scores 0–100: up to 60 points from goal-specific metric coverage (metrics tagged to 6+ goals count at 0.4 weight), up to 25 from the business description and up to 15 from impact themes. High confidence needs ≥50 points and at least one goal-specific metric. Own-footprint metrics (OI4112, OI9604, OI1479, OI1697) are disclosure, not contribution, and count at the reduced weight.</t>
         </is>
       </c>
     </row>
@@ -3691,48 +4686,84 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Risk (0–100) weights claim–metric gaps (30%), missing negative impacts (20%), vague language (20%), selective reporting (15%) and lack of verification (15%). 60+ is flagged for review.</t>
+          <t>Risk (0–100) weights claim–metric gaps (30%), missing negative impacts (20%), vague language (20%), selective reporting (15%) and lack of verification (15%). Bands: ≤20 Genuine Impact Leader; ≤40 Substantive with Gaps; ≤60 Moderate Risk; ≤80 High Risk; ≤100 Probable Greenwashing.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>IC gate</t>
+          <t>Version</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Applies the fund thesis thresholds. Failures caused by missing data are reported as insufficient evidence, not as a negative finding.</t>
+          <t>Methodology v1.1.0 · config 8fabf9b5a7e2 (effective 2026-10-07).</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Standards</t>
+          <t>Gap analysis</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>IRIS+ 5.3c catalog, IMP Five Dimensions, UN SDG framework (17 goals, 169 targets).</t>
+          <t>Coverage is the share of the sector's IRIS+ core metric set the company reports.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>IC gate</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Applies the fund thesis thresholds. Failures caused by missing data are reported as insufficient evidence, not as a negative finding.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Standards</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>IRIS+ 5.3c catalog, IMP Five Dimensions, UN SDG framework (17 goals, 169 targets).</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>Schema</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>Export schema version 1.0. Numeric cells are numbers; '—' marks values that were not reported.</t>
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>AI use</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Automated analysis: produced by rules and a deterministic scoring model; no generative AI was used. 4 of 22 scores are estimated from document text rather than reported metrics. Review before relying on it.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B9"/>
+  <autoFilter ref="A1:B12"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/demo/kampung_makmur_sdn_bhd/kampung_makmur_sdn_bhd_data.xlsx
+++ b/demo/kampung_makmur_sdn_bhd/kampung_makmur_sdn_bhd_data.xlsx
@@ -527,7 +527,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-07T00:37:32Z</t>
+          <t>2026-10-07T00:54:56Z</t>
         </is>
       </c>
     </row>
@@ -2245,7 +2245,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-10-07T00:37:32Z</t>
+          <t>2026-10-07T00:54:56Z</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>

--- a/demo/kampung_makmur_sdn_bhd/kampung_makmur_sdn_bhd_data.xlsx
+++ b/demo/kampung_makmur_sdn_bhd/kampung_makmur_sdn_bhd_data.xlsx
@@ -527,7 +527,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-07T00:54:56Z</t>
+          <t>2026-10-07T01:08:36Z</t>
         </is>
       </c>
     </row>
@@ -733,7 +733,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Reporting 2 metrics (1 theme-specific, 25 available)</t>
+          <t>2 metrics reported · 1 of 25 reference metrics</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Reporting 3 metrics (1 theme-specific, 10 available)</t>
+          <t>3 metrics reported · 1 of 10 reference metrics</t>
         </is>
       </c>
     </row>
@@ -817,7 +817,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Estimated from sector/description (4 metrics available to track)</t>
+          <t>Estimated from sector/description · 4 reference metrics to track</t>
         </is>
       </c>
     </row>
@@ -2245,7 +2245,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-10-07T00:54:56Z</t>
+          <t>2026-10-07T01:08:36Z</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Reporting 2 metrics (1 theme-specific, 25 available)</t>
+          <t>2 metrics reported · 1 of 25 reference metrics</t>
         </is>
       </c>
       <c r="E7" s="5" t="n">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Reporting 3 metrics (1 theme-specific, 10 available)</t>
+          <t>3 metrics reported · 1 of 10 reference metrics</t>
         </is>
       </c>
       <c r="E8" s="5" t="n">
@@ -2476,7 +2476,7 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Estimated from sector/description (4 metrics available to track)</t>
+          <t>Estimated from sector/description · 4 reference metrics to track</t>
         </is>
       </c>
       <c r="E11" s="5" t="n">

--- a/demo/kampung_makmur_sdn_bhd/kampung_makmur_sdn_bhd_data.xlsx
+++ b/demo/kampung_makmur_sdn_bhd/kampung_makmur_sdn_bhd_data.xlsx
@@ -527,7 +527,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-07T01:08:36Z</t>
+          <t>2026-10-08T15:56:18Z</t>
         </is>
       </c>
     </row>
@@ -574,7 +574,7 @@
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="12">
@@ -596,7 +596,7 @@
         </is>
       </c>
       <c r="B13" s="4" t="n">
-        <v>49</v>
+        <v>38</v>
       </c>
     </row>
     <row r="14">
@@ -627,7 +627,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Automated analysis: produced by rules and a deterministic scoring model; no generative AI was used. 4 of 22 scores are estimated from document text rather than reported metrics. Review before relying on it.</t>
+          <t>Automated analysis: produced by rules and a deterministic scoring model; no generative AI was used. 3 of 22 scores are estimated from document text rather than reported metrics. Review before relying on it.</t>
         </is>
       </c>
     </row>
@@ -639,7 +639,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1.1.0</t>
+          <t>1.2.0</t>
         </is>
       </c>
     </row>
@@ -651,7 +651,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>8fabf9b5a7e2</t>
+          <t>ae3e77ecaccf</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="C3" t="n">
         <v>3</v>
@@ -765,7 +765,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="C4" t="n">
         <v>4</v>
@@ -775,7 +775,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Scale=1.5, Depth=1.5, Duration=1.5</t>
+          <t>Scale=1.7, Depth=1.7, Duration=1.7</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         </is>
       </c>
       <c r="C3" s="4" t="n">
-        <v>41.7</v>
+        <v>39.2</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="C4" s="4" t="n">
-        <v>41.7</v>
+        <v>36.7</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -998,15 +998,15 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Responsible Consumption and Production</t>
+          <t>Clean Water and Sanitation</t>
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>32.5</v>
+        <v>30</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1019,23 +1019,19 @@
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>12.2, 12.3, 12.4, 12.6</t>
-        </is>
-      </c>
+      <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Life on Land</t>
+          <t>Gender Equality</t>
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>32.5</v>
+        <v>27.7</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1047,20 +1043,28 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>OI6213</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>5.1, 5.2, 5.5</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Decent Work and Economic Growth</t>
+          <t>Responsible Consumption and Production</t>
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>32.3</v>
+        <v>27.5</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1072,28 +1076,24 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>OI6213, OI8869</t>
-        </is>
-      </c>
+      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>8.1, 8.2, 8.3, 8.4, 8.5, 8.6, 8.7, 8.8</t>
+          <t>12.2, 12.3, 12.4, 12.6</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Clean Water and Sanitation</t>
+          <t>Life on Land</t>
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>30</v>
+        <v>27.5</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1110,15 +1110,15 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>No Poverty</t>
+          <t>Decent Work and Economic Growth</t>
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>25</v>
+        <v>27.3</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1130,53 +1130,61 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>OI6213, OI8869</t>
+        </is>
+      </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1.4, 1.5</t>
+          <t>8.1, 8.2, 8.3, 8.4, 8.5, 8.6, 8.7, 8.8</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Good Health and Well-being</t>
+          <t>No Poverty</t>
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>17.5</v>
+        <v>25</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>1.4, 1.5</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Partnerships for the Goals</t>
+          <t>Quality Education</t>
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>17.5</v>
+        <v>22.5</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1189,15 +1197,15 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Industry, Innovation and Infrastructure</t>
+          <t>Good Health and Well-being</t>
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>14</v>
+        <v>17.5</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1209,28 +1217,20 @@
           <t>no</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>OI8869</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>9.3, 9.4</t>
-        </is>
-      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Gender Equality</t>
+          <t>Industry, Innovation and Infrastructure</t>
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>10.2</v>
+        <v>14</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1244,26 +1244,26 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>OI6213</t>
+          <t>OI8869</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>5.1, 5.2, 5.5</t>
+          <t>9.3, 9.4</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Reduced Inequalities</t>
+          <t>Partnerships for the Goals</t>
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1276,19 +1276,15 @@
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>10.1, 10.2, 10.3</t>
-        </is>
-      </c>
+      <c r="G14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Sustainable Cities and Communities</t>
+          <t>Reduced Inequalities</t>
         </is>
       </c>
       <c r="C15" s="4" t="n">
@@ -1307,17 +1303,17 @@
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>11.5, 11.6</t>
+          <t>10.1, 10.2, 10.3</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Life Below Water</t>
+          <t>Sustainable Cities and Communities</t>
         </is>
       </c>
       <c r="C16" s="4" t="n">
@@ -1334,15 +1330,19 @@
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>11.5, 11.6</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Peace, Justice and Strong Institutions</t>
+          <t>Life Below Water</t>
         </is>
       </c>
       <c r="C17" s="4" t="n">
@@ -1363,15 +1363,15 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Quality Education</t>
+          <t>Peace, Justice and Strong Institutions</t>
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>OD4091</t>
+          <t>PI7852</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Social and Environmental Targets</t>
+          <t>Payments to Supplier Individuals: Smallholder</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
@@ -1577,12 +1577,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>OI1075</t>
+          <t>OI6709</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Board of Directors: Total</t>
+          <t>Waste Produced: Total</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
@@ -1600,12 +1600,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>OI1479</t>
+          <t>OI6912</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Greenhouse Gas Emissions: Total</t>
+          <t>Land Directly Controlled: Sustainably Managed</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
@@ -1623,12 +1623,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>OI1571</t>
+          <t>OI9891</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Full-time Employees: Female Managers</t>
+          <t>Pesticide Use</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
@@ -1646,12 +1646,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>OI1582</t>
+          <t>OI3757</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Wage Equity</t>
+          <t>Occupational Injuries</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
@@ -1669,12 +1669,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>OI3757</t>
+          <t>OI4112</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Occupational Injuries</t>
+          <t>Greenhouse Gas Emissions: Direct (Scope 1)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
@@ -1692,12 +1692,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>OI4112</t>
+          <t>OI4724</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Greenhouse Gas Emissions: Direct (Scope 1)</t>
+          <t>Workers Earning a Living Wage or Higher</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
@@ -1715,12 +1715,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>OI4724</t>
+          <t>OI1479</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Workers Earning a Living Wage or Higher</t>
+          <t>Greenhouse Gas Emissions: Total</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
@@ -1738,12 +1738,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>OI4732</t>
+          <t>OI1582</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Social and Environmental Performance Reporting</t>
+          <t>Wage Equity</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>OI6709</t>
+          <t>OD4091</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Waste Produced: Total</t>
+          <t>Social and Environmental Targets</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
@@ -1784,12 +1784,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>OI6912</t>
+          <t>OI1075</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Land Directly Controlled: Sustainably Managed</t>
+          <t>Board of Directors: Total</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
@@ -1807,12 +1807,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>OI9891</t>
+          <t>OI4732</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Pesticide Use</t>
+          <t>Social and Environmental Performance Reporting</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
@@ -1830,12 +1830,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>PI7852</t>
+          <t>OI1571</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Payments to Supplier Individuals: Smallholder</t>
+          <t>Full-time Employees: Female Managers</t>
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
@@ -2245,7 +2245,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-10-07T01:08:36Z</t>
+          <t>2026-10-08T15:56:18Z</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
@@ -2264,7 +2264,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Automated analysis: produced by rules and a deterministic scoring model; no generative AI was used. 4 of 22 scores are estimated from document text rather than reported metrics. Review before relying on it.</t>
+          <t>Automated analysis: produced by rules and a deterministic scoring model; no generative AI was used. 3 of 22 scores are estimated from document text rather than reported metrics. Review before relying on it.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.1.0</t>
+          <t>1.2.0</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>config 8fabf9b5a7e2</t>
+          <t>config ae3e77ecaccf</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
@@ -2311,11 +2311,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.7/5.0</t>
+          <t>1.8/5.0</t>
         </is>
       </c>
       <c r="E6" s="5" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="F6" s="6" t="n">
         <v>5</v>
@@ -2372,7 +2372,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2.3/5.0</t>
+          <t>2.5/5.0</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -2381,7 +2381,7 @@
         </is>
       </c>
       <c r="E8" s="5" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="F8" s="6" t="n">
         <v>5</v>
@@ -2405,16 +2405,16 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.5/5.0</t>
+          <t>1.7/5.0</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Scale=1.5, Depth=1.5, Duration=1.5</t>
+          <t>Scale=1.7, Depth=1.7, Duration=1.7</t>
         </is>
       </c>
       <c r="E9" s="5" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="F9" s="6" t="n">
         <v>5</v>
@@ -2537,7 +2537,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>41.7/100</t>
+          <t>39.2/100</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2546,7 +2546,7 @@
         </is>
       </c>
       <c r="E13" s="5" t="n">
-        <v>41.7</v>
+        <v>39.2</v>
       </c>
       <c r="F13" s="6" t="n">
         <v>100</v>
@@ -2570,7 +2570,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>41.7/100</t>
+          <t>36.7/100</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2579,7 +2579,7 @@
         </is>
       </c>
       <c r="E14" s="5" t="n">
-        <v>41.7</v>
+        <v>36.7</v>
       </c>
       <c r="F14" s="6" t="n">
         <v>100</v>
@@ -2598,12 +2598,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SDG 12</t>
+          <t>SDG 6</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>32.5/100</t>
+          <t>30.0/100</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2612,7 +2612,7 @@
         </is>
       </c>
       <c r="E15" s="5" t="n">
-        <v>32.5</v>
+        <v>30</v>
       </c>
       <c r="F15" s="6" t="n">
         <v>100</v>
@@ -2631,21 +2631,21 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SDG 15</t>
+          <t>SDG 5</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>32.5/100</t>
+          <t>27.7/100</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">medium | metrics: </t>
+          <t>medium | metrics: OI6213</t>
         </is>
       </c>
       <c r="E16" s="5" t="n">
-        <v>32.5</v>
+        <v>27.7</v>
       </c>
       <c r="F16" s="6" t="n">
         <v>100</v>
@@ -2664,21 +2664,21 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SDG 8</t>
+          <t>SDG 12</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>32.3/100</t>
+          <t>27.5/100</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>medium | metrics: OI6213,OI8869</t>
+          <t xml:space="preserve">medium | metrics: </t>
         </is>
       </c>
       <c r="E17" s="5" t="n">
-        <v>32.3</v>
+        <v>27.5</v>
       </c>
       <c r="F17" s="6" t="n">
         <v>100</v>
@@ -2697,12 +2697,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SDG 6</t>
+          <t>SDG 15</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>30.0/100</t>
+          <t>27.5/100</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2711,7 +2711,7 @@
         </is>
       </c>
       <c r="E18" s="5" t="n">
-        <v>30</v>
+        <v>27.5</v>
       </c>
       <c r="F18" s="6" t="n">
         <v>100</v>
@@ -2730,21 +2730,21 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SDG 1</t>
+          <t>SDG 8</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>25.0/100</t>
+          <t>27.3/100</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">medium | metrics: </t>
+          <t>medium | metrics: OI6213,OI8869</t>
         </is>
       </c>
       <c r="E19" s="5" t="n">
-        <v>25</v>
+        <v>27.3</v>
       </c>
       <c r="F19" s="6" t="n">
         <v>100</v>
@@ -2763,21 +2763,21 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SDG 3</t>
+          <t>SDG 1</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>17.5/100</t>
+          <t>25.0/100</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">low | metrics: </t>
+          <t xml:space="preserve">medium | metrics: </t>
         </is>
       </c>
       <c r="E20" s="5" t="n">
-        <v>17.5</v>
+        <v>25</v>
       </c>
       <c r="F20" s="6" t="n">
         <v>100</v>
@@ -2796,21 +2796,21 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SDG 17</t>
+          <t>SDG 4</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>17.5/100</t>
+          <t>22.5/100</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">low | metrics: </t>
+          <t xml:space="preserve">medium | metrics: </t>
         </is>
       </c>
       <c r="E21" s="5" t="n">
-        <v>17.5</v>
+        <v>22.5</v>
       </c>
       <c r="F21" s="6" t="n">
         <v>100</v>
@@ -2829,21 +2829,21 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SDG 9</t>
+          <t>SDG 3</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>14.0/100</t>
+          <t>17.5/100</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>low | metrics: OI8869</t>
+          <t xml:space="preserve">low | metrics: </t>
         </is>
       </c>
       <c r="E22" s="5" t="n">
-        <v>14</v>
+        <v>17.5</v>
       </c>
       <c r="F22" s="6" t="n">
         <v>100</v>
@@ -2862,21 +2862,21 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SDG 5</t>
+          <t>SDG 9</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>10.2/100</t>
+          <t>14.0/100</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>low | metrics: OI6213</t>
+          <t>low | metrics: OI8869</t>
         </is>
       </c>
       <c r="E23" s="5" t="n">
-        <v>10.2</v>
+        <v>14</v>
       </c>
       <c r="F23" s="6" t="n">
         <v>100</v>
@@ -2895,12 +2895,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>SDG 10</t>
+          <t>SDG 17</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>10.0/100</t>
+          <t>10.5/100</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2909,7 +2909,7 @@
         </is>
       </c>
       <c r="E24" s="5" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="F24" s="6" t="n">
         <v>100</v>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>SDG 11</t>
+          <t>SDG 10</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2961,7 +2961,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>SDG 14</t>
+          <t>SDG 11</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2994,7 +2994,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>SDG 16</t>
+          <t>SDG 14</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3027,12 +3027,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>SDG 4</t>
+          <t>SDG 16</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>5.0/100</t>
+          <t>10.0/100</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="E28" s="5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F28" s="6" t="n">
         <v>100</v>
@@ -3065,16 +3065,16 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>49.0/100</t>
+          <t>38.0/100</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Moderate Risk</t>
+          <t>Substantive with Gaps</t>
         </is>
       </c>
       <c r="E29" s="5" t="n">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="F29" s="6" t="n">
         <v>100</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>OD4091</t>
+          <t>PI7852</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -3132,7 +3132,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Social and Environmental Targets</t>
+          <t>Payments to Supplier Individuals: Smallholder</t>
         </is>
       </c>
       <c r="G31" t="inlineStr"/>
@@ -3168,7 +3168,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>OI1075</t>
+          <t>OI6709</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -3178,7 +3178,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Board of Directors: Total</t>
+          <t>Waste Produced: Total</t>
         </is>
       </c>
       <c r="G33" t="inlineStr"/>
@@ -3191,7 +3191,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>OI1479</t>
+          <t>OI6912</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -3201,7 +3201,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Greenhouse Gas Emissions: Total</t>
+          <t>Land Directly Controlled: Sustainably Managed</t>
         </is>
       </c>
       <c r="G34" t="inlineStr"/>
@@ -3214,7 +3214,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>OI1571</t>
+          <t>OI9891</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -3224,7 +3224,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Full-time Employees: Female Managers</t>
+          <t>Pesticide Use</t>
         </is>
       </c>
       <c r="G35" t="inlineStr"/>
@@ -3237,7 +3237,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>OI1582</t>
+          <t>OI3757</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -3247,7 +3247,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Wage Equity</t>
+          <t>Occupational Injuries</t>
         </is>
       </c>
       <c r="G36" t="inlineStr"/>
@@ -3260,7 +3260,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>OI3757</t>
+          <t>OI4112</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -3270,7 +3270,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Occupational Injuries</t>
+          <t>Greenhouse Gas Emissions: Direct (Scope 1)</t>
         </is>
       </c>
       <c r="G37" t="inlineStr"/>
@@ -3283,7 +3283,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>OI4112</t>
+          <t>OI4724</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -3293,7 +3293,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Greenhouse Gas Emissions: Direct (Scope 1)</t>
+          <t>Workers Earning a Living Wage or Higher</t>
         </is>
       </c>
       <c r="G38" t="inlineStr"/>
@@ -3306,7 +3306,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>OI4724</t>
+          <t>OI1479</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -3316,7 +3316,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Workers Earning a Living Wage or Higher</t>
+          <t>Greenhouse Gas Emissions: Total</t>
         </is>
       </c>
       <c r="G39" t="inlineStr"/>
@@ -3329,7 +3329,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>OI4732</t>
+          <t>OI1582</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -3339,7 +3339,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Social and Environmental Performance Reporting</t>
+          <t>Wage Equity</t>
         </is>
       </c>
       <c r="G40" t="inlineStr"/>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>OI6709</t>
+          <t>OD4091</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3362,7 +3362,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Waste Produced: Total</t>
+          <t>Social and Environmental Targets</t>
         </is>
       </c>
       <c r="G41" t="inlineStr"/>
@@ -3375,7 +3375,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>OI6912</t>
+          <t>OI1075</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3385,7 +3385,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Land Directly Controlled: Sustainably Managed</t>
+          <t>Board of Directors: Total</t>
         </is>
       </c>
       <c r="G42" t="inlineStr"/>
@@ -3398,7 +3398,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>OI9891</t>
+          <t>OI4732</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3408,7 +3408,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Pesticide Use</t>
+          <t>Social and Environmental Performance Reporting</t>
         </is>
       </c>
       <c r="G43" t="inlineStr"/>
@@ -3421,7 +3421,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>PI7852</t>
+          <t>OI1571</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3431,7 +3431,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Payments to Supplier Individuals: Smallholder</t>
+          <t>Full-time Employees: Female Managers</t>
         </is>
       </c>
       <c r="G44" t="inlineStr"/>
@@ -3791,7 +3791,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>Automated analysis: produced by rules and a deterministic scoring model; no generative AI was used. 4 of 22 scores are estimated from document text rather than reported metrics. Review before relying on it.</t>
+          <t>Automated analysis: produced by rules and a deterministic scoring model; no generative AI was used. 3 of 22 scores are estimated from document text rather than reported metrics. Review before relying on it.</t>
         </is>
       </c>
     </row>
@@ -3875,7 +3875,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>4 of 22</t>
+          <t>3 of 22</t>
         </is>
       </c>
     </row>
@@ -4009,13 +4009,13 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>evidence: estimated</t>
+          <t>evidence: partial</t>
         </is>
       </c>
     </row>
@@ -4162,7 +4162,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SDG 12 alignment</t>
+          <t>SDG 6 alignment</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4190,7 +4190,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SDG 15 alignment</t>
+          <t>SDG 5 alignment</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4218,7 +4218,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SDG 8 alignment</t>
+          <t>SDG 12 alignment</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -4246,7 +4246,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>SDG 6 alignment</t>
+          <t>SDG 15 alignment</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -4274,7 +4274,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>SDG 1 alignment</t>
+          <t>SDG 8 alignment</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -4302,7 +4302,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>SDG 3 alignment</t>
+          <t>SDG 1 alignment</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -4330,7 +4330,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>SDG 17 alignment</t>
+          <t>SDG 4 alignment</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -4345,20 +4345,20 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>basis: estimated</t>
+          <t>basis: core_set</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>SDG 9 alignment</t>
+          <t>SDG 3 alignment</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -4386,7 +4386,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SDG 5 alignment</t>
+          <t>SDG 9 alignment</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -4414,7 +4414,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>SDG 10 alignment</t>
+          <t>SDG 17 alignment</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -4429,20 +4429,20 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
-          <t>basis: core_set</t>
+          <t>basis: estimated</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SDG 11 alignment</t>
+          <t>SDG 10 alignment</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -4470,7 +4470,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>SDG 14 alignment</t>
+          <t>SDG 11 alignment</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4498,7 +4498,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SDG 16 alignment</t>
+          <t>SDG 14 alignment</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4526,7 +4526,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>SDG 4 alignment</t>
+          <t>SDG 16 alignment</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4698,7 +4698,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Methodology v1.1.0 · config 8fabf9b5a7e2 (effective 2026-10-07).</t>
+          <t>Methodology v1.2.0 · config ae3e77ecaccf (effective 2026-10-08).</t>
         </is>
       </c>
     </row>
@@ -4758,7 +4758,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Automated analysis: produced by rules and a deterministic scoring model; no generative AI was used. 4 of 22 scores are estimated from document text rather than reported metrics. Review before relying on it.</t>
+          <t>Automated analysis: produced by rules and a deterministic scoring model; no generative AI was used. 3 of 22 scores are estimated from document text rather than reported metrics. Review before relying on it.</t>
         </is>
       </c>
     </row>

--- a/demo/kampung_makmur_sdn_bhd/kampung_makmur_sdn_bhd_data.xlsx
+++ b/demo/kampung_makmur_sdn_bhd/kampung_makmur_sdn_bhd_data.xlsx
@@ -527,7 +527,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-08T15:56:18Z</t>
+          <t>2026-10-08T16:14:39Z</t>
         </is>
       </c>
     </row>
@@ -2245,7 +2245,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-10-08T15:56:18Z</t>
+          <t>2026-10-08T16:14:39Z</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>

--- a/demo/kampung_makmur_sdn_bhd/kampung_makmur_sdn_bhd_data.xlsx
+++ b/demo/kampung_makmur_sdn_bhd/kampung_makmur_sdn_bhd_data.xlsx
@@ -527,7 +527,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-08T16:14:39Z</t>
+          <t>2026-10-08T19:52:58Z</t>
         </is>
       </c>
     </row>
@@ -2245,7 +2245,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-10-08T16:14:39Z</t>
+          <t>2026-10-08T19:52:58Z</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>

--- a/demo/kampung_makmur_sdn_bhd/kampung_makmur_sdn_bhd_data.xlsx
+++ b/demo/kampung_makmur_sdn_bhd/kampung_makmur_sdn_bhd_data.xlsx
@@ -527,7 +527,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-08T19:52:58Z</t>
+          <t>2026-10-08T20:03:42Z</t>
         </is>
       </c>
     </row>
@@ -2245,7 +2245,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-10-08T19:52:58Z</t>
+          <t>2026-10-08T20:03:42Z</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>

--- a/demo/kampung_makmur_sdn_bhd/kampung_makmur_sdn_bhd_data.xlsx
+++ b/demo/kampung_makmur_sdn_bhd/kampung_makmur_sdn_bhd_data.xlsx
@@ -527,7 +527,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-08T20:03:42Z</t>
+          <t>2026-10-09T05:01:53Z</t>
         </is>
       </c>
     </row>
@@ -574,7 +574,7 @@
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="12">
@@ -786,7 +786,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
@@ -796,7 +796,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Depth=1.3, Duration=1.3</t>
+          <t>Depth=1.9, Duration=1.9</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -2245,7 +2245,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-10-08T20:03:42Z</t>
+          <t>2026-10-09T05:01:53Z</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
@@ -2311,11 +2311,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.8/5.0</t>
+          <t>1.9/5.0</t>
         </is>
       </c>
       <c r="E6" s="5" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="F6" s="6" t="n">
         <v>5</v>
@@ -2438,16 +2438,16 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.3/5.0</t>
+          <t>1.9/5.0</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Depth=1.3, Duration=1.3</t>
+          <t>Depth=1.9, Duration=1.9</t>
         </is>
       </c>
       <c r="E10" s="5" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="F10" s="6" t="n">
         <v>5</v>

--- a/demo/kampung_makmur_sdn_bhd/kampung_makmur_sdn_bhd_data.xlsx
+++ b/demo/kampung_makmur_sdn_bhd/kampung_makmur_sdn_bhd_data.xlsx
@@ -527,7 +527,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-09T05:01:53Z</t>
+          <t>2026-10-09T09:37:38Z</t>
         </is>
       </c>
     </row>
@@ -2245,7 +2245,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-10-09T05:01:53Z</t>
+          <t>2026-10-09T09:37:38Z</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
